--- a/modules/internal_policy_drafter/docs/2026-09-15_销售行为管理办法修订_07_条款级原文对照清单.xlsx
+++ b/modules/internal_policy_drafter/docs/2026-09-15_销售行为管理办法修订_07_条款级原文对照清单.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录 G" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录 H" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录 I" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录 J" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1713,12 +1714,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>第三十八条（按内容定位，供参考）</t>
+          <t>第二十七条</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>第三十八条国家机关为履行法定职责的需要收集、使用数据，应当在其履行法定职责的范围内依照法律、行政法规规定的条件和程序进行；对在履行职责中知悉的个人隐私、个人信息、商业秘密、保密商务信息等数据应当依法予以保密，不得泄露或者非法向他人提供。</t>
+          <t>第二十七条开展数据处理活动应当依照法律、法规的规定，建立健全全流程数据安全管理制度，组织开展数据安全教育培训，采取相应的技术措施和其他必要措施，保障数据安全。利用互联网等信息网络开展数据处理活动，应当在网络安全等级保护制度的基础上，履行上述数据安全保护义务。重要数据的处理者应当明确数据安全负责人和管理机构，落实数据安全保护责任。</t>
         </is>
       </c>
       <c r="I31" s="4" t="n"/>
@@ -1886,12 +1887,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>第四条</t>
+          <t>第六条</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>第四条本指导意见所称重大群体性事件，是指因销售误导问题引发50名以上投保人集体上访、静坐或其他过激行为，或者因销售误导问题引发人身保险公司或其代理机构一个营业场所内同时出现30名以上投保人集中退保，以及其他中国保监会认为应当采取应急处置措施的突发事件。重大群体性事件分为三个响应层级。其中，三级响应是指因销售误导问题引发50名以上100名以下投保人集体上访、静坐或其他过激行为，或者人身保险公司或其代理机构一个营业场所突发出现30名以上100名以下投保人集中退保，或非正常退保金额超过3000万元；二级响应是指因销售误导问题引发100名以上500名以下投保人集体上访、静坐或其他过激行为，或者人身保险公司或其代理机构一个营业场所突发出现100名以上500名以下投保人集中退保，或非正常退保金额超过1亿元；一级响应是指因销售误导问题引发500名以上投保人集体上访、静坐或其他过激行为，或者人身保险公司或其代理机构一个营业场所突发出现500名以上投保人集中退保，或非正常退保金额超过5亿元，或因集中退保金额巨大导致保险公司出现支付困难，以及其他影响较为恶劣，中国保监会认为应当采取应急处置措施的突发事件。</t>
+          <t>第六条保险公司进行销售误导责任追究，应当按照“责任明确、程序合法、权责对等、逐级追究”的原则，根据销售误导问题性质、情节及损失程度，综合考虑社会影响，在摸清事实的基础上，根据相关人员承担的责任予以追究。</t>
         </is>
       </c>
       <c r="I36" s="4" t="n"/>
@@ -5742,12 +5743,12 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>第十五条</t>
+          <t>第十条</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>第十五条保险公司应当在犹豫期内对合同期限超过一年的人身保险新单业务进行回访，并及时记录回访情况。回访应当包括以下内容：（一）确认受访人是否为投保人本人；（二）确认投保人是否购买了该保险产品以及投保人和被保险人是否按照要求亲笔签名；（三）确认投保人是否已经阅读并理解产品说明书和投保提示的内容；（四）确认投保人是否知悉保险责任、责任免除和保险期间；（五）确认投保人是否知悉退保可能受到的损失；（六）确认投保人是否知悉犹豫期的起算时间、期间以及享有的权利；（七）采用期缴方式的，确认投保人是否了解缴费期间和缴费频率。人身保险新型产品的回访，中国保监会另有规定的，从其规定。</t>
+          <t>第十条投保人提交的投保单填写错误或者所附资料不完整的，保险公司应当自收到投保资料之日起5 个工作日内一次性告知投保人需要补正或者补充的内容。</t>
         </is>
       </c>
       <c r="I132" s="5" t="n"/>
@@ -6461,12 +6462,12 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>第四十三条</t>
+          <t>第四十四条</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>第四十三条违反本办法</t>
+          <t>第四十四条保险公司、保险中介机构、保险销售人员违反本办法规定和金融监管总局关于财产保险、人身保险、保险中介销售管理的其他相关规定，情节严重或者造成严重后果的，由金融监管总局及其派出机构依照法律、行政法规进行处罚；法律、行政法规没有规定的，金融监管总局及其派出机构可以视情况给予警告或者通报批评，处以一万元以上十万元以下罚款。</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -7520,6 +7521,438 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>① 条号自洽性</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>「监管文件条款」列所标条号 与 「条款原文」首部实际条号 逐项比对</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>**0 处不符**</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>② 条号存在性</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>引用条号是否超出该依据文件实际条数（取自附录 A）</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>**0 处越界**</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>③ 原文与源一致性</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>依据行原文与**五源语料中该文件该条的实际正文**逐字比对（回源核验）</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>可比对 **109 项全部一致**，0 不符、0 缺条</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>④ 原文完整性</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>依据原文长度与结构完整性</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>**1 处原文残缺**（已修复）</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>⑤ 主题对应性</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>制度条款全文 vs 该依据文件**全部条文**的条级相关性排名，识别「实际引用条文排名靠后且存在明显更贴切条文」的情形</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>**4 处确证错误**（已修复）；另登记存疑项</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>条款</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>原引</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>改引</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>认定理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>第57条</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>第43条</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>**第44条**</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>原引第四十三条在语料中正文残缺（仅「第四十三条 违反本办法」10 字），不足以支撑「违规问责」；第四十四条为本办法完整的处罚条款，且与该条制度条款「违规问责」直接对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>第47条</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>R-34</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>第15条</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>**第10条**</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>原引第十五条为「犹豫期回访」，属回访管理，与本条款「保单送达与查询服务」主题不符；第十条与该条制度条款「需要补正投保资料的，公司应当自收到投保资料…」逐字对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>第10条</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>R-35</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>第4条</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>**第6条**</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>原引第四条为「重大群体性事件」的定义性条款，不承载责任追究义务；第六条为销售误导责任追究的原则性规定，与本条款「建立内部责任追究机制」直接对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>第9条</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>R-29</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>第38条</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>**第27条**</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>原引第三十八条主体为**国家机关**（履行法定职责收集使用数据），与保险公司作为数据处理者的义务无关；第二十七条为数据处理者的一般义务条款，与本条款「建立健全个人信息保护机制、完善管理制度和操作流程」对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>条款</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>所引条文主题</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>与条款的关系</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>第42条</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>R-04 第7条</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>开展互联网保险业务的保险机构及其自营网络平台应具备的条件</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>制度条款为「互联网销售可回溯管理」，该条为平台准入条件，属**上位/前置要求**而非可回溯要求本身</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>保留并标注为前置条件依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>第44条</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>R-01 第31条</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>保险公司、保险中介机构应当采取录音录像等方法对保险产品销售行为实施可回溯管理</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>制度条款为「录音录像内容要求」，该条为可回溯管理的**总括性授权依据**</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>保留（总括依据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>第54条</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>R-01 第8条</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>保险公司、保险中介机构应当履行销售管理主体责任</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>制度条款为「内部监督检查」，该条为**主体责任的上位依据**，监督检查属其落实方式</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>第9条</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>R-26 第13条</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>处理个人信息的合法性基础（取得同意等六种情形）</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>与制度条款「未经个人同意不得向他人提供其信息」**直接相关**</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>保留（核验后确认对应成立）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>第10条</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>R-18 第6条</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>人身保险业务活动中不得有的欺骗行为（七项）</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>与制度条款「落实销售误导行为认定」直接相关</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>保留（核验后确认对应成立）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
